--- a/data/ETCHE/functionsETCHE.xlsx
+++ b/data/ETCHE/functionsETCHE.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lochmannm\Documents\GitHub\Hessen_END_Healthiar\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\GitHub Repository\Hessen_END_Healthiar\data\ETCHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A262D3FA-C83F-4EAF-AB37-6FE9E5EE4C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8484D3-AB46-45B6-BAEC-CC15FA2AC982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1980" windowWidth="29040" windowHeight="17520" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Anmerkungen" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="59">
   <si>
     <t>Guski et al. (2017)</t>
   </si>
@@ -84,18 +85,12 @@
     <t>-50.9693 + 1.0168 * c + 0.0072 * c^2</t>
   </si>
   <si>
-    <t>Miedema and Vos</t>
-  </si>
-  <si>
     <t>High sleep disturbance</t>
   </si>
   <si>
     <t>19.4312 - 0.9336 * c + 0.0126 * c^2</t>
   </si>
   <si>
-    <t>Basner and McGuire</t>
-  </si>
-  <si>
     <t>67.5406 - 3.1852 * c + 0.0391 * c^2</t>
   </si>
   <si>
@@ -187,6 +182,39 @@
   </si>
   <si>
     <t>100*ifelse (c &gt;= threshold, 1 / (1 + exp(-(log(0.1 / 0.9) + (log(1.38) / 10 * (c - 50))))), 0.1)</t>
+  </si>
+  <si>
+    <t>Miedema and Vos (2004)</t>
+  </si>
+  <si>
+    <t>Basner and McGuire (2018)</t>
+  </si>
+  <si>
+    <t>Miedema and Vos (2007)</t>
+  </si>
+  <si>
+    <t>END_model</t>
+  </si>
+  <si>
+    <t>1 - "Ja"</t>
+  </si>
+  <si>
+    <t>0 - "Nein"</t>
+  </si>
+  <si>
+    <t>Codierung</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Offenes</t>
+  </si>
+  <si>
+    <t>für END_model fehlt IHD</t>
   </si>
 </sst>
 </file>
@@ -296,8 +324,8 @@
       <xdr:rowOff>23091</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>686177</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4162802</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>65624</xdr:rowOff>
     </xdr:to>
@@ -340,8 +368,8 @@
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>521724</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2464824</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>133482</xdr:rowOff>
     </xdr:to>
@@ -380,9 +408,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -420,7 +448,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -526,7 +554,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -668,7 +696,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -676,21 +704,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8156CAC4-1F63-4625-9494-276B4F46068B}">
-  <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="77.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -702,27 +742,30 @@
         <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+      <c r="K1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -740,21 +783,24 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -772,21 +818,24 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -804,27 +853,30 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
         <v>3</v>
@@ -833,30 +885,33 @@
         <v>45</v>
       </c>
       <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="J5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
         <v>4</v>
@@ -865,30 +920,33 @@
         <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
         <v>4</v>
@@ -897,30 +955,33 @@
         <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
         <v>4</v>
@@ -929,30 +990,33 @@
         <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G9" t="s">
         <v>4</v>
@@ -961,30 +1025,33 @@
         <v>40</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
         <v>3</v>
@@ -993,27 +1060,30 @@
         <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
         <v>3</v>
@@ -1022,27 +1092,30 @@
         <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
         <v>3</v>
@@ -1051,27 +1124,30 @@
         <v>45</v>
       </c>
       <c r="I12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
         <v>3</v>
@@ -1080,27 +1156,30 @@
         <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
         <v>3</v>
@@ -1109,27 +1188,30 @@
         <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
         <v>3</v>
@@ -1138,27 +1220,30 @@
         <v>45</v>
       </c>
       <c r="I15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G16" t="s">
         <v>3</v>
@@ -1167,27 +1252,30 @@
         <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G17" t="s">
         <v>3</v>
@@ -1196,27 +1284,30 @@
         <v>45</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G18" t="s">
         <v>3</v>
@@ -1225,27 +1316,30 @@
         <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>29</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
         <v>3</v>
@@ -1254,14 +1348,66 @@
         <v>50</v>
       </c>
       <c r="I19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1566883E-42F0-44A5-A5A7-BA00A033D6E6}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/ETCHE/functionsETCHE.xlsx
+++ b/data/ETCHE/functionsETCHE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\GitHub Repository\Hessen_END_Healthiar\data\ETCHE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lochmannm\Documents\GitHub\END2DALY\data\ETCHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8484D3-AB46-45B6-BAEC-CC15FA2AC982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A800516-53D4-4F8D-8997-F2F359AD34B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
+    <workbookView xWindow="28680" yWindow="-4140" windowWidth="29040" windowHeight="15720" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="68">
   <si>
     <t>Guski et al. (2017)</t>
   </si>
@@ -215,6 +215,33 @@
   </si>
   <si>
     <t>für END_model fehlt IHD</t>
+  </si>
+  <si>
+    <t>ETCHE23_model</t>
+  </si>
+  <si>
+    <t>ETCHE24_model</t>
+  </si>
+  <si>
+    <t>Behavioural problems</t>
+  </si>
+  <si>
+    <t>Overweight</t>
+  </si>
+  <si>
+    <t>ifelse(c&gt;threshold,(c-threshold)*1.073,0)</t>
+  </si>
+  <si>
+    <t>ifelse(c&gt;threshold,(c-threshold)*1.063,0)</t>
+  </si>
+  <si>
+    <t>Engelmann ETC HE Report 2024/11, ch 3.3.2</t>
+  </si>
+  <si>
+    <t>Engelmann ETC HE Report 2024/11</t>
+  </si>
+  <si>
+    <t>Engelmann ETC HE Report 2024/11, ch 3.3.5</t>
   </si>
 </sst>
 </file>
@@ -274,14 +301,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>349250</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>153755</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>77555</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>83846</xdr:rowOff>
     </xdr:to>
@@ -306,8 +333,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8731250" y="0"/>
-          <a:ext cx="9710505" cy="9135771"/>
+          <a:off x="18830925" y="0"/>
+          <a:ext cx="9707330" cy="9132596"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -318,16 +345,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>704272</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>23091</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>416095</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>93501</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>4162802</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>65624</xdr:rowOff>
+      <xdr:colOff>2254628</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123333</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -350,8 +377,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1466272" y="4271818"/>
-          <a:ext cx="6839905" cy="2810267"/>
+          <a:off x="416095" y="4934442"/>
+          <a:ext cx="6993239" cy="2725594"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -363,15 +390,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>391832</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>173692</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2464824</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>133482</xdr:rowOff>
+      <xdr:colOff>2812206</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>26279</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -394,12 +421,73 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="47625" y="7153275"/>
-          <a:ext cx="7335274" cy="943107"/>
+          <a:off x="391832" y="7524751"/>
+          <a:ext cx="7575080" cy="934702"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3650961</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>141720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>30694</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>31462</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Grafik 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4C9C822-88BB-25CF-DAA5-67684AA255AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8811779" y="5337175"/>
+          <a:ext cx="6756499" cy="2837007"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -704,22 +792,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8156CAC4-1F63-4625-9494-276B4F46068B}">
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="77.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="77.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -753,8 +841,14 @@
       <c r="K1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -788,8 +882,14 @@
       <c r="K2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -823,8 +923,14 @@
       <c r="K3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -858,8 +964,14 @@
       <c r="K4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -893,8 +1005,14 @@
       <c r="K5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -928,8 +1046,14 @@
       <c r="K6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -963,8 +1087,14 @@
       <c r="K7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -998,8 +1128,14 @@
       <c r="K8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1033,8 +1169,14 @@
       <c r="K9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1065,8 +1207,14 @@
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1097,8 +1245,14 @@
       <c r="K11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1129,8 +1283,14 @@
       <c r="K12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1161,8 +1321,14 @@
       <c r="K13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1193,8 +1359,14 @@
       <c r="K14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1225,8 +1397,14 @@
       <c r="K15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1257,8 +1435,14 @@
       <c r="K16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1289,8 +1473,14 @@
       <c r="K17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1321,8 +1511,14 @@
       <c r="K18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1355,6 +1551,316 @@
       </c>
       <c r="K19">
         <v>0</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>50</v>
+      </c>
+      <c r="I20" t="s">
+        <v>66</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21">
+        <v>50</v>
+      </c>
+      <c r="I21" t="s">
+        <v>66</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>45</v>
+      </c>
+      <c r="I22" t="s">
+        <v>65</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>45</v>
+      </c>
+      <c r="I23" t="s">
+        <v>65</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>45</v>
+      </c>
+      <c r="I24" t="s">
+        <v>65</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H25">
+        <v>45</v>
+      </c>
+      <c r="I25" t="s">
+        <v>67</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26">
+        <v>45</v>
+      </c>
+      <c r="I26" t="s">
+        <v>67</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27">
+        <v>45</v>
+      </c>
+      <c r="I27" t="s">
+        <v>67</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1366,14 +1872,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1566883E-42F0-44A5-A5A7-BA00A033D6E6}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>55</v>
       </c>
@@ -1381,7 +1887,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>51</v>
       </c>
@@ -1389,7 +1895,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>51</v>
       </c>
@@ -1397,12 +1903,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>58</v>
       </c>

--- a/data/ETCHE/functionsETCHE.xlsx
+++ b/data/ETCHE/functionsETCHE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lochmannm\Documents\GitHub\END2DALY\data\ETCHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A800516-53D4-4F8D-8997-F2F359AD34B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC3836B-4E1F-47A2-A1AA-F4E7E33D08AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-4140" windowWidth="29040" windowHeight="15720" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="68">
   <si>
     <t>Guski et al. (2017)</t>
   </si>
@@ -1587,6 +1587,9 @@
       <c r="I20" t="s">
         <v>66</v>
       </c>
+      <c r="J20" t="s">
+        <v>46</v>
+      </c>
       <c r="K20">
         <v>0</v>
       </c>
@@ -1624,6 +1627,9 @@
       </c>
       <c r="I21" t="s">
         <v>66</v>
+      </c>
+      <c r="J21" t="s">
+        <v>46</v>
       </c>
       <c r="K21">
         <v>0</v>

--- a/data/ETCHE/functionsETCHE.xlsx
+++ b/data/ETCHE/functionsETCHE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lochmannm\Documents\GitHub\END2DALY\data\ETCHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC3836B-4E1F-47A2-A1AA-F4E7E33D08AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C65F40B-D845-4720-9A07-F6E3AE218AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4140" windowWidth="29040" windowHeight="15720" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
+    <workbookView xWindow="-28920" yWindow="-1980" windowWidth="29040" windowHeight="17520" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="67">
   <si>
     <t>Guski et al. (2017)</t>
   </si>
@@ -76,27 +76,9 @@
     <t>High noise annoyance</t>
   </si>
   <si>
-    <t>78.9270 - 3.1162 * c + 0.0342 * c^2</t>
-  </si>
-  <si>
-    <t>38.1596 - 2.05538 * c + 0.0285 * c^2</t>
-  </si>
-  <si>
-    <t>-50.9693 + 1.0168 * c + 0.0072 * c^2</t>
-  </si>
-  <si>
     <t>High sleep disturbance</t>
   </si>
   <si>
-    <t>19.4312 - 0.9336 * c + 0.0126 * c^2</t>
-  </si>
-  <si>
-    <t>67.5406 - 3.1852 * c + 0.0391 * c^2</t>
-  </si>
-  <si>
-    <t>16.7885 - 0.9293 * c + 0.0198 * c^2</t>
-  </si>
-  <si>
     <t>Engelmann et al. (2025), ch. 3.3.1</t>
   </si>
   <si>
@@ -142,21 +124,6 @@
     <t>threshold</t>
   </si>
   <si>
-    <t>1 - abs(72 - (-126.52 + c * 2.49) / sqrt(2054.43))</t>
-  </si>
-  <si>
-    <t>1 - abs(72 - (-90.70 + c * 1.80) / sqrt(1789 + 272))</t>
-  </si>
-  <si>
-    <t>ifelse(c&gt;threshold,(c-threshold)*1.055,0)</t>
-  </si>
-  <si>
-    <t>ifelse(c&gt;threshold,(c-threshold)*1.032,0)</t>
-  </si>
-  <si>
-    <t>ifelse(c&gt;threshold,(c-threshold)*1.062,0)</t>
-  </si>
-  <si>
     <t>population_type</t>
   </si>
   <si>
@@ -181,9 +148,6 @@
     <t>0.006</t>
   </si>
   <si>
-    <t>100*ifelse (c &gt;= threshold, 1 / (1 + exp(-(log(0.1 / 0.9) + (log(1.38) / 10 * (c - 50))))), 0.1)</t>
-  </si>
-  <si>
     <t>Miedema and Vos (2004)</t>
   </si>
   <si>
@@ -229,12 +193,6 @@
     <t>Overweight</t>
   </si>
   <si>
-    <t>ifelse(c&gt;threshold,(c-threshold)*1.073,0)</t>
-  </si>
-  <si>
-    <t>ifelse(c&gt;threshold,(c-threshold)*1.063,0)</t>
-  </si>
-  <si>
     <t>Engelmann ETC HE Report 2024/11, ch 3.3.2</t>
   </si>
   <si>
@@ -242,6 +200,45 @@
   </si>
   <si>
     <t>Engelmann ETC HE Report 2024/11, ch 3.3.5</t>
+  </si>
+  <si>
+    <t>exp(log(1.055)/10*(c-threshold))</t>
+  </si>
+  <si>
+    <t>exp(log(1.032)/10*(c-threshold))</t>
+  </si>
+  <si>
+    <t>exp(log(1.062)/10*(c-threshold))</t>
+  </si>
+  <si>
+    <t>exp(log(1.073)/10*(c-threshold))</t>
+  </si>
+  <si>
+    <t>exp(log(1.063)/10*(c-threshold))</t>
+  </si>
+  <si>
+    <t>ifelse (c &gt;= threshold, 1 / (1 + exp(-(log(0.1 / 0.9) + (log(1.38) / 10 * (c - 50))))), 0.1)</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>(78.9270 - 3.1162 * c + 0.0342 * c^2)/100</t>
+  </si>
+  <si>
+    <t>(38.1596 - 2.05538 * c + 0.0285 * c^2)/100</t>
+  </si>
+  <si>
+    <t>(-50.9693 + 1.0168 * c + 0.0072 * c^2)/100</t>
+  </si>
+  <si>
+    <t>(19.4312 - 0.9336 * c + 0.0126 * c^2)/100</t>
+  </si>
+  <si>
+    <t>(67.5406 - 3.1852 * c + 0.0391 * c^2)/100</t>
+  </si>
+  <si>
+    <t>(16.7885 - 0.9293 * c + 0.0198 * c^2)/100</t>
   </si>
 </sst>
 </file>
@@ -812,13 +809,13 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -830,22 +827,22 @@
         <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s">
         <v>32</v>
       </c>
-      <c r="J1" t="s">
-        <v>43</v>
-      </c>
       <c r="K1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="L1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="M1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -853,19 +850,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
         <v>3</v>
@@ -877,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -894,19 +891,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
         <v>3</v>
@@ -918,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -935,19 +932,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
         <v>3</v>
@@ -959,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -976,19 +973,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
         <v>3</v>
@@ -997,10 +994,10 @@
         <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1014,22 +1011,22 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
         <v>4</v>
@@ -1038,10 +1035,10 @@
         <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1055,22 +1052,22 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="G7" t="s">
         <v>4</v>
@@ -1079,10 +1076,10 @@
         <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1096,22 +1093,22 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
         <v>4</v>
@@ -1120,10 +1117,10 @@
         <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J8" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1137,22 +1134,22 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
         <v>4</v>
@@ -1161,10 +1158,10 @@
         <v>40</v>
       </c>
       <c r="I9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1178,22 +1175,22 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
         <v>3</v>
@@ -1202,7 +1199,7 @@
         <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1216,22 +1213,22 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G11" t="s">
         <v>3</v>
@@ -1240,7 +1237,7 @@
         <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -1254,22 +1251,22 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G12" t="s">
         <v>3</v>
@@ -1278,7 +1275,7 @@
         <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1292,22 +1289,22 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
         <v>3</v>
@@ -1316,7 +1313,7 @@
         <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1330,22 +1327,22 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
         <v>3</v>
@@ -1354,7 +1351,7 @@
         <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1368,22 +1365,22 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
         <v>3</v>
@@ -1392,7 +1389,7 @@
         <v>45</v>
       </c>
       <c r="I15" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1406,22 +1403,22 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G16" t="s">
         <v>3</v>
@@ -1430,7 +1427,7 @@
         <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1444,22 +1441,22 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G17" t="s">
         <v>3</v>
@@ -1468,7 +1465,7 @@
         <v>45</v>
       </c>
       <c r="I17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1482,22 +1479,22 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
         <v>3</v>
@@ -1506,7 +1503,7 @@
         <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1520,22 +1517,22 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G19" t="s">
         <v>3</v>
@@ -1544,10 +1541,10 @@
         <v>50</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1561,22 +1558,22 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G20" t="s">
         <v>3</v>
@@ -1585,10 +1582,10 @@
         <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="J20" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1602,22 +1599,22 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
         <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G21" t="s">
         <v>3</v>
@@ -1626,10 +1623,10 @@
         <v>50</v>
       </c>
       <c r="I21" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="J21" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1643,22 +1640,22 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
         <v>3</v>
@@ -1667,7 +1664,7 @@
         <v>45</v>
       </c>
       <c r="I22" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1681,22 +1678,22 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
         <v>3</v>
@@ -1705,7 +1702,7 @@
         <v>45</v>
       </c>
       <c r="I23" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1719,22 +1716,22 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
         <v>3</v>
@@ -1743,7 +1740,7 @@
         <v>45</v>
       </c>
       <c r="I24" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1757,22 +1754,22 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G25" t="s">
         <v>3</v>
@@ -1781,7 +1778,7 @@
         <v>45</v>
       </c>
       <c r="I25" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1795,22 +1792,22 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G26" t="s">
         <v>3</v>
@@ -1819,7 +1816,7 @@
         <v>45</v>
       </c>
       <c r="I26" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -1833,22 +1830,22 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G27" t="s">
         <v>3</v>
@@ -1857,7 +1854,7 @@
         <v>45</v>
       </c>
       <c r="I27" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -1882,41 +1879,41 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/data/ETCHE/functionsETCHE.xlsx
+++ b/data/ETCHE/functionsETCHE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lochmannm\Documents\GitHub\END2DALY\data\ETCHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C65F40B-D845-4720-9A07-F6E3AE218AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2262A98E-BA7F-4C98-BC97-BFE65101BA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1980" windowWidth="29040" windowHeight="17520" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
   </bookViews>
@@ -202,6 +202,30 @@
     <t>Engelmann ETC HE Report 2024/11, ch 3.3.5</t>
   </si>
   <si>
+    <t>ifelse (c &gt;= threshold, 1 / (1 + exp(-(log(0.1 / 0.9) + (log(1.38) / 10 * (c - 50))))), 0.1)</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>(78.9270 - 3.1162 * c + 0.0342 * c^2)/100</t>
+  </si>
+  <si>
+    <t>(38.1596 - 2.05538 * c + 0.0285 * c^2)/100</t>
+  </si>
+  <si>
+    <t>(-50.9693 + 1.0168 * c + 0.0072 * c^2)/100</t>
+  </si>
+  <si>
+    <t>(19.4312 - 0.9336 * c + 0.0126 * c^2)/100</t>
+  </si>
+  <si>
+    <t>(67.5406 - 3.1852 * c + 0.0391 * c^2)/100</t>
+  </si>
+  <si>
+    <t>(16.7885 - 0.9293 * c + 0.0198 * c^2)/100</t>
+  </si>
+  <si>
     <t>exp(log(1.055)/10*(c-threshold))</t>
   </si>
   <si>
@@ -215,30 +239,6 @@
   </si>
   <si>
     <t>exp(log(1.063)/10*(c-threshold))</t>
-  </si>
-  <si>
-    <t>ifelse (c &gt;= threshold, 1 / (1 + exp(-(log(0.1 / 0.9) + (log(1.38) / 10 * (c - 50))))), 0.1)</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>(78.9270 - 3.1162 * c + 0.0342 * c^2)/100</t>
-  </si>
-  <si>
-    <t>(38.1596 - 2.05538 * c + 0.0285 * c^2)/100</t>
-  </si>
-  <si>
-    <t>(-50.9693 + 1.0168 * c + 0.0072 * c^2)/100</t>
-  </si>
-  <si>
-    <t>(19.4312 - 0.9336 * c + 0.0126 * c^2)/100</t>
-  </si>
-  <si>
-    <t>(67.5406 - 3.1852 * c + 0.0391 * c^2)/100</t>
-  </si>
-  <si>
-    <t>(16.7885 - 0.9293 * c + 0.0198 * c^2)/100</t>
   </si>
 </sst>
 </file>
@@ -862,7 +862,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
         <v>3</v>
@@ -903,7 +903,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
         <v>3</v>
@@ -944,7 +944,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G4" t="s">
         <v>3</v>
@@ -985,7 +985,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G5" t="s">
         <v>3</v>
@@ -1026,7 +1026,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
         <v>4</v>
@@ -1067,7 +1067,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G7" t="s">
         <v>4</v>
@@ -1108,7 +1108,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G8" t="s">
         <v>4</v>
@@ -1149,7 +1149,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
         <v>4</v>
@@ -1190,7 +1190,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G10" t="s">
         <v>3</v>
@@ -1228,7 +1228,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G11" t="s">
         <v>3</v>
@@ -1266,7 +1266,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
         <v>3</v>
@@ -1304,7 +1304,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G13" t="s">
         <v>3</v>
@@ -1342,7 +1342,7 @@
         <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G14" t="s">
         <v>3</v>
@@ -1380,7 +1380,7 @@
         <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
         <v>3</v>
@@ -1418,7 +1418,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G16" t="s">
         <v>3</v>
@@ -1456,7 +1456,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
         <v>3</v>
@@ -1494,7 +1494,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G18" t="s">
         <v>3</v>
@@ -1532,7 +1532,7 @@
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G19" t="s">
         <v>3</v>
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G20" t="s">
         <v>3</v>
@@ -1614,7 +1614,7 @@
         <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G21" t="s">
         <v>3</v>
@@ -1655,7 +1655,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G22" t="s">
         <v>3</v>
@@ -1693,7 +1693,7 @@
         <v>6</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G23" t="s">
         <v>3</v>
@@ -1731,7 +1731,7 @@
         <v>7</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G24" t="s">
         <v>3</v>
@@ -1769,7 +1769,7 @@
         <v>5</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G25" t="s">
         <v>3</v>
@@ -1807,7 +1807,7 @@
         <v>6</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G26" t="s">
         <v>3</v>
@@ -1845,7 +1845,7 @@
         <v>7</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
         <v>3</v>

--- a/data/ETCHE/functionsETCHE.xlsx
+++ b/data/ETCHE/functionsETCHE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lochmannm\Documents\GitHub\END2DALY\data\ETCHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2262A98E-BA7F-4C98-BC97-BFE65101BA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F12B17F-8E0E-491B-87F7-A6E217FD63A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1980" windowWidth="29040" windowHeight="17520" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="70">
   <si>
     <t>Guski et al. (2017)</t>
   </si>
@@ -239,6 +239,15 @@
   </si>
   <si>
     <t>exp(log(1.063)/10*(c-threshold))</t>
+  </si>
+  <si>
+    <t>IHD</t>
+  </si>
+  <si>
+    <t>exp(log(1.08)/10*(c-threshold))</t>
+  </si>
+  <si>
+    <t>END</t>
   </si>
 </sst>
 </file>
@@ -298,13 +307,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>276225</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>77555</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>83846</xdr:rowOff>
@@ -344,13 +353,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>416095</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>93501</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>2254628</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>123333</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -388,13 +397,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>391832</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>173692</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>2812206</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>26279</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -432,13 +441,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3650961</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>141720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>30694</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>31462</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -789,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8156CAC4-1F63-4625-9494-276B4F46068B}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -1000,7 +1009,7 @@
         <v>33</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -1164,7 +1173,7 @@
         <v>34</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -1403,7 +1412,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -1418,22 +1427,22 @@
         <v>5</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G16" t="s">
         <v>3</v>
       </c>
       <c r="H16">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1453,7 +1462,7 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>64</v>
@@ -1491,7 +1500,7 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>64</v>
@@ -1517,34 +1526,31 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
       </c>
-      <c r="F19" t="s">
-        <v>54</v>
+      <c r="F19" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="G19" t="s">
         <v>3</v>
       </c>
       <c r="H19">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1553,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -1570,7 +1576,7 @@
         <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
         <v>54</v>
@@ -1582,7 +1588,7 @@
         <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s">
         <v>35</v>
@@ -1591,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20">
         <v>1</v>
@@ -1611,7 +1617,7 @@
         <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
         <v>54</v>
@@ -1640,10 +1646,10 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
@@ -1654,17 +1660,20 @@
       <c r="E22" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>65</v>
+      <c r="F22" t="s">
+        <v>54</v>
       </c>
       <c r="G22" t="s">
         <v>3</v>
       </c>
       <c r="H22">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I22" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="J22" t="s">
+        <v>35</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1690,7 +1699,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>65</v>
@@ -1728,7 +1737,7 @@
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>65</v>
@@ -1754,7 +1763,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -1766,10 +1775,10 @@
         <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G25" t="s">
         <v>3</v>
@@ -1778,7 +1787,7 @@
         <v>45</v>
       </c>
       <c r="I25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1804,7 +1813,7 @@
         <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>66</v>
@@ -1842,7 +1851,7 @@
         <v>23</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>66</v>
@@ -1863,6 +1872,44 @@
         <v>0</v>
       </c>
       <c r="M27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" t="s">
+        <v>3</v>
+      </c>
+      <c r="H28">
+        <v>45</v>
+      </c>
+      <c r="I28" t="s">
+        <v>53</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>1</v>
       </c>
     </row>

--- a/data/ETCHE/functionsETCHE.xlsx
+++ b/data/ETCHE/functionsETCHE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lochmannm\Documents\GitHub\END2DALY\data\ETCHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F12B17F-8E0E-491B-87F7-A6E217FD63A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93268994-1CC7-4ED7-B661-B9A73AB4346E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1980" windowWidth="29040" windowHeight="17520" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
   </bookViews>
@@ -46,9 +46,6 @@
     <t>outcome</t>
   </si>
   <si>
-    <t>source</t>
-  </si>
-  <si>
     <t>lden</t>
   </si>
   <si>
@@ -248,6 +245,9 @@
   </si>
   <si>
     <t>END</t>
+  </si>
+  <si>
+    <t>noise_source</t>
   </si>
 </sst>
 </file>
@@ -818,63 +818,63 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" t="s">
-        <v>26</v>
-      </c>
       <c r="J1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" t="s">
         <v>47</v>
-      </c>
-      <c r="M1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>45</v>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -897,25 +897,25 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>45</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -938,25 +938,25 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -979,34 +979,34 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1020,34 +1020,34 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1061,34 +1061,34 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1102,34 +1102,34 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1143,34 +1143,34 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <v>40</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1184,31 +1184,31 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1222,31 +1222,31 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -1260,31 +1260,31 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1298,31 +1298,31 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1336,31 +1336,31 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1374,31 +1374,31 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>45</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1412,31 +1412,31 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="G16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16">
         <v>53</v>
       </c>
       <c r="I16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1450,31 +1450,31 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17">
         <v>45</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1488,31 +1488,31 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1526,31 +1526,31 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1564,34 +1564,34 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20">
         <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1605,34 +1605,34 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21">
         <v>50</v>
       </c>
       <c r="I21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1646,34 +1646,34 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22">
         <v>50</v>
       </c>
       <c r="I22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1687,31 +1687,31 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>45</v>
       </c>
       <c r="I23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1725,31 +1725,31 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>45</v>
       </c>
       <c r="I24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1763,31 +1763,31 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>45</v>
       </c>
       <c r="I25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1801,31 +1801,31 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26">
         <v>45</v>
       </c>
       <c r="I26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -1839,31 +1839,31 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G27" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27">
         <v>45</v>
       </c>
       <c r="I27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -1877,31 +1877,31 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <v>45</v>
       </c>
       <c r="I28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -1926,41 +1926,41 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
         <v>43</v>
-      </c>
-      <c r="C2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
         <v>39</v>
-      </c>
-      <c r="C3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/ETCHE/functionsETCHE.xlsx
+++ b/data/ETCHE/functionsETCHE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lochmannm\Documents\GitHub\END2DALY\data\ETCHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93268994-1CC7-4ED7-B661-B9A73AB4346E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07A66CD-6C1A-45F9-AF22-3B157F4F80C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1980" windowWidth="29040" windowHeight="17520" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="71">
   <si>
     <t>Guski et al. (2017)</t>
   </si>
@@ -202,9 +202,6 @@
     <t>ifelse (c &gt;= threshold, 1 / (1 + exp(-(log(0.1 / 0.9) + (log(1.38) / 10 * (c - 50))))), 0.1)</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>(78.9270 - 3.1162 * c + 0.0342 * c^2)/100</t>
   </si>
   <si>
@@ -248,6 +245,12 @@
   </si>
   <si>
     <t>noise_source</t>
+  </si>
+  <si>
+    <t>1-pnorm((72-(-126.52+c*2.49))/sqrt(2054.43))</t>
+  </si>
+  <si>
+    <t>1-pnorm((72-(-90.70+(c)*(1.80)))/sqrt(1789+272))</t>
   </si>
 </sst>
 </file>
@@ -316,7 +319,7 @@
       <xdr:col>27</xdr:col>
       <xdr:colOff>77555</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>83846</xdr:rowOff>
+      <xdr:rowOff>87021</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -358,9 +361,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2254628</xdr:colOff>
+      <xdr:colOff>2257803</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>123333</xdr:rowOff>
+      <xdr:rowOff>126508</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -402,9 +405,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2812206</xdr:colOff>
+      <xdr:colOff>2809031</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>26279</xdr:rowOff>
+      <xdr:rowOff>29454</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -446,9 +449,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>30694</xdr:colOff>
+      <xdr:colOff>27519</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>31462</xdr:rowOff>
+      <xdr:rowOff>28287</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -827,7 +830,7 @@
         <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F1" t="s">
         <v>9</v>
@@ -871,7 +874,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
@@ -912,7 +915,7 @@
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
         <v>2</v>
@@ -953,7 +956,7 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4" t="s">
         <v>2</v>
@@ -994,7 +997,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G5" t="s">
         <v>2</v>
@@ -1035,7 +1038,7 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
         <v>3</v>
@@ -1076,7 +1079,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7" t="s">
         <v>3</v>
@@ -1117,7 +1120,7 @@
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8" t="s">
         <v>3</v>
@@ -1158,7 +1161,7 @@
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G9" t="s">
         <v>3</v>
@@ -1198,8 +1201,8 @@
       <c r="E10" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>61</v>
+      <c r="F10" t="s">
+        <v>60</v>
       </c>
       <c r="G10" t="s">
         <v>2</v>
@@ -1236,8 +1239,8 @@
       <c r="E11" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>61</v>
+      <c r="F11" t="s">
+        <v>60</v>
       </c>
       <c r="G11" t="s">
         <v>2</v>
@@ -1274,8 +1277,8 @@
       <c r="E12" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>61</v>
+      <c r="F12" t="s">
+        <v>60</v>
       </c>
       <c r="G12" t="s">
         <v>2</v>
@@ -1313,7 +1316,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
         <v>2</v>
@@ -1351,7 +1354,7 @@
         <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
         <v>2</v>
@@ -1389,7 +1392,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" t="s">
         <v>2</v>
@@ -1412,7 +1415,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
@@ -1427,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
         <v>2</v>
@@ -1436,7 +1439,7 @@
         <v>53</v>
       </c>
       <c r="I16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1465,7 +1468,7 @@
         <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17" t="s">
         <v>2</v>
@@ -1503,7 +1506,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
         <v>2</v>
@@ -1541,7 +1544,7 @@
         <v>6</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
         <v>2</v>
@@ -1702,7 +1705,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G23" t="s">
         <v>2</v>
@@ -1740,7 +1743,7 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
         <v>2</v>
@@ -1778,7 +1781,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G25" t="s">
         <v>2</v>
@@ -1816,7 +1819,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G26" t="s">
         <v>2</v>
@@ -1854,7 +1857,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G27" t="s">
         <v>2</v>
@@ -1892,7 +1895,7 @@
         <v>6</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G28" t="s">
         <v>2</v>
